--- a/online_experiment/online_exp2/crowding_stationary_dynamic_flies_online_singleSideStim.xlsx
+++ b/online_experiment/online_exp2/crowding_stationary_dynamic_flies_online_singleSideStim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fh986/Documents/Github/crowded-dynamic-fixation/online_experiment/online_exp2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/helenhu/Documents/GitHub/crowded-dynamic-fixation/online_experiment/online_exp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116A672F-FD51-5340-90A5-4FC9361EC489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E06160-10A4-C644-AE82-384B602A6CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="40960" windowHeight="23040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="700" windowWidth="26160" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="124">
   <si>
     <t>_about</t>
   </si>
@@ -44,15 +44,6 @@
   </si>
   <si>
     <t>blockShuffleGroups1</t>
-  </si>
-  <si>
-    <t>Stationary</t>
-  </si>
-  <si>
-    <t>Dynamic</t>
-  </si>
-  <si>
-    <t>Flies</t>
   </si>
   <si>
     <t>calibrateScreenSizeBool</t>
@@ -865,31 +856,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B6" s="1" t="b">
         <v>1</v>
@@ -897,7 +888,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B7" s="1" t="b">
         <v>0</v>
@@ -908,20 +899,20 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B10" s="1">
         <v>6</v>
@@ -929,31 +920,31 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B14" s="1">
         <v>60</v>
@@ -961,7 +952,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1">
         <v>5</v>
@@ -969,15 +960,15 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B17" s="1">
         <v>15</v>
@@ -985,7 +976,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B18" s="1" t="b">
         <v>0</v>
@@ -993,7 +984,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B19" s="1" t="b">
         <v>0</v>
@@ -1001,34 +992,34 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
@@ -1041,7 +1032,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B25" s="1" t="b">
         <v>1</v>
@@ -1111,27 +1102,27 @@
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="P27" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="R27" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="S27" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T27" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
@@ -1190,66 +1181,66 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="R29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="S29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C30" t="b">
         <v>1</v>
@@ -1308,7 +1299,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C31" t="b">
         <v>1</v>
@@ -1367,66 +1358,66 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
         <v>14</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
         <v>15</v>
       </c>
-      <c r="D32" t="s">
+      <c r="G32" t="s">
         <v>16</v>
       </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>17</v>
       </c>
-      <c r="F32" t="s">
+      <c r="I32" t="s">
         <v>18</v>
       </c>
-      <c r="G32" t="s">
+      <c r="J32" t="s">
         <v>19</v>
       </c>
-      <c r="H32" t="s">
+      <c r="K32" t="s">
         <v>20</v>
       </c>
-      <c r="I32" t="s">
+      <c r="L32" t="s">
         <v>21</v>
       </c>
-      <c r="J32" t="s">
+      <c r="M32" t="s">
         <v>22</v>
       </c>
-      <c r="K32" t="s">
+      <c r="N32" t="s">
         <v>23</v>
       </c>
-      <c r="L32" t="s">
+      <c r="O32" t="s">
         <v>24</v>
       </c>
-      <c r="M32" t="s">
+      <c r="P32" t="s">
         <v>25</v>
       </c>
-      <c r="N32" t="s">
+      <c r="Q32" t="s">
         <v>26</v>
       </c>
-      <c r="O32" t="s">
+      <c r="R32" t="s">
         <v>27</v>
       </c>
-      <c r="P32" t="s">
+      <c r="S32" t="s">
         <v>28</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="T32" t="s">
         <v>29</v>
-      </c>
-      <c r="R32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S32" t="s">
-        <v>31</v>
-      </c>
-      <c r="T32" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -1485,330 +1476,330 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="P35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="R35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="T35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="R36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="S36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="T36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="398" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="I37" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="J37" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="K37" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="L37" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="M37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="O37" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="P37" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="L37" s="4" t="s">
+      <c r="Q37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R37" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="M37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="N37" s="4" t="s">
+      <c r="S37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="T37" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="O37" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="R37" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="S37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="T37" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="O40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="R40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="T40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1867,7 +1858,7 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1926,7 +1917,7 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C43" t="b">
         <v>1</v>
@@ -1985,7 +1976,7 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C44">
         <v>0.15</v>
@@ -2044,66 +2035,66 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="R45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="S45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="T45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>0.5</v>
@@ -2162,7 +2153,7 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2221,7 +2212,7 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2280,7 +2271,7 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C49" t="b">
         <v>1</v>
@@ -2339,7 +2330,7 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C50" t="b">
         <v>1</v>
@@ -2398,7 +2389,7 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>1.25</v>
@@ -2457,7 +2448,7 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>0.75</v>
@@ -2516,7 +2507,7 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>30</v>
@@ -2575,7 +2566,7 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C54" t="b">
         <v>1</v>
@@ -2634,7 +2625,7 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C55" t="b">
         <v>0</v>
@@ -2693,7 +2684,7 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C56" t="b">
         <v>1</v>
@@ -2752,7 +2743,7 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>0.15</v>
@@ -2811,7 +2802,7 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>10</v>
@@ -2870,7 +2861,7 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2929,125 +2920,125 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="S60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="T60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="R61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="S61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="T61" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C62">
         <v>0.02</v>
@@ -3106,7 +3097,7 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -3165,66 +3156,66 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="S64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="T64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C65">
         <v>0.7</v>
@@ -3283,7 +3274,7 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C66">
         <v>1.2</v>
@@ -3342,7 +3333,7 @@
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C67">
         <v>40</v>
@@ -3402,7 +3393,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A27:T28 A67:T67 A30:B30 A31:T32 A1:T2 A40:T62 A39:B39 G39:H39 Q39:T39 A34:T36 A33:B33 K39:N39 A38:T38 A37:B37 A64:T65 A63:B63 A26:C26" numberStoredAsText="1"/>
+    <ignoredError sqref="A28:T28 A67:T67 A30:B30 A31:T32 A1:T2 A40:T62 A39:B39 G39:H39 Q39:T39 A34:T36 A33:B33 K39:N39 A38:T38 A37:B37 A64:T65 A63:B63 A26:C26 A27:N27" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>